--- a/scripts/relacao_grupos.xlsx
+++ b/scripts/relacao_grupos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\tr.alienigenaV5-main\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5507735-A0CC-4F31-8D44-EE05AE76EA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57DF02D-3871-4167-A5E4-348258462137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0B20066D-6251-4453-9D31-2904E3C38042}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
   <si>
     <t>Grupo</t>
   </si>
@@ -109,6 +109,24 @@
   </si>
   <si>
     <t>Caçambeiros</t>
+  </si>
+  <si>
+    <t>Galera do Escolar</t>
+  </si>
+  <si>
+    <t>Motoristas de Busão</t>
+  </si>
+  <si>
+    <t>Dudu</t>
+  </si>
+  <si>
+    <t>Caçamba e Operador</t>
+  </si>
+  <si>
+    <t>Caçambeiro e Operador</t>
+  </si>
+  <si>
+    <t>Laércio</t>
   </si>
 </sst>
 </file>
@@ -460,11 +478,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8EFB24A-3C34-4AA9-81CF-1BE1A2C43323}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
@@ -639,6 +658,40 @@
         <v>88996851562</v>
       </c>
     </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11">
+        <v>88988561241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12">
+        <v>88992792964</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
